--- a/data/exports/contribution_screen/contribution-screen-05.xlsx
+++ b/data/exports/contribution_screen/contribution-screen-05.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A2:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -483,7 +483,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WHAT NOT TO DO. Do not mark a paper out_of_scope because it proposes no technique. Benchmarks, surveys and measurement studies all belong in the corpus. AgentDojo proposes no defense and is the harness this project's own experiments run on. out_of_scope means the paper is not about untrustworthy context at all.</t>
+          <t>WHAT NOT TO DO. Do not mark a paper out_of_scope because it proposes no technique. Benchmarks, surveys and measurement studies all belong in the corpus. out_of_scope means the paper is not about untrustworthy context at all.</t>
         </is>
       </c>
     </row>
@@ -493,38 +493,38 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
+          <t>THE COLUMN THAT MATTERS MOST IS names_registry_technique. A paper can be a harness and still name attacks. AgentDojo is an evaluation environment AND it names seven injections; 38 of the 349 confirmed (defense, attack) pairs in this study depend on them, so it is a contributing paper by any rule. WebArena is also a harness and names none. Genre does not decide this. Read the paper's section headings and tables and answer what it NAMES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
           <t>Where to look, in this order:</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   1. the abstract and the contributions list  -&gt; contribution, origin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   2. the EVALUATION or EXPERIMENTS section    -&gt; evaluated_against</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">   3. related work                             -&gt; parent_technique</t>
+          <t xml:space="preserve">   1. the abstract and the contributions list  -&gt; contribution, origin</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2. the EVALUATION or EXPERIMENTS section    -&gt; evaluated_against</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Do not answer from the introduction alone. An introduction saying 'we address context rot' is not evidence that context rot was measured. That specific confusion is what this pass exists to find.</t>
+          <t xml:space="preserve">   3. related work                             -&gt; parent_technique</t>
         </is>
       </c>
     </row>
@@ -532,9 +532,9 @@
       <c r="A16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Every row needs a verbatim quote. No quote, no entry.</t>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Do not answer from the introduction alone. An introduction saying 'we address context rot' is not evidence that context rot was measured. That specific confusion is what this pass exists to find.</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,17 @@
       <c r="A18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Every row needs a verbatim quote. No quote, no entry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Sheets: 'contribution' = the eleven values and what each one means. 'fields' = what each column wants. 'papers' = your list, one row each.</t>
         </is>
@@ -782,7 +792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -912,7 +922,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>belongs_in_corpus</t>
+          <t>names_registry_technique</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -922,22 +932,56 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>no ONLY for out_of_scope. A benchmark, a survey and a measurement study all belong. If unsure, say unsure and explain in notes.</t>
+          <t>THE AGENTDOJO QUESTION. Does this paper name a specific attack or failure mode that other papers then cite and test against, even if the paper is a benchmark, a harness or a survey? AgentDojo is a harness AND it names seven injections that 38 confirmed pairs depend on, so the answer for it is yes. WebArena is a harness that names none, so no. Answer from the paper's own section headings and tables, not from its genre.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>named_techniques</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>free text</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>If names_registry_technique is yes, list them as the paper names them, semicolon separated. 'important-instructions injection; ignore-previous injection'. Blank otherwise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>belongs_in_corpus</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>yes / no / unsure</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>no ONLY for out_of_scope. A benchmark, a survey and a measurement study all belong. If unsure, say unsure and explain in notes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>free text</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Anything that does not fit above, especially disagreement with the current coding.</t>
         </is>
@@ -954,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P61"/>
+  <dimension ref="A1:R61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -971,8 +1015,10 @@
     <col width="22" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
     <col width="44" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="34" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1048,10 +1094,20 @@
       </c>
       <c r="O1" s="3" t="inlineStr">
         <is>
+          <t>names_registry_technique</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>named_techniques</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
           <t>belongs_in_corpus</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>notes</t>
         </is>

--- a/data/exports/contribution_screen/contribution-screen-05.xlsx
+++ b/data/exports/contribution_screen/contribution-screen-05.xlsx
@@ -932,7 +932,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>THE AGENTDOJO QUESTION. Does this paper name a specific attack or failure mode that other papers then cite and test against, even if the paper is a benchmark, a harness or a survey? AgentDojo is a harness AND it names seven injections that 38 confirmed pairs depend on, so the answer for it is yes. WebArena is a harness that names none, so no. Answer from the paper's own section headings and tables, not from its genre.</t>
+          <t>THE AGENTDOJO QUESTION. Narrower than its name: does this paper name a specific ATTACK or FAILURE MODE that other papers then cite and test against, even though the paper is a benchmark, a harness or a survey? AgentDojo is a harness AND it names seven injections that 38 confirmed pairs depend on, so yes. WebArena is a harness and names none, so no. A paper that names only its own DEFENSE is 'no' here, and that is correct: it is already protected by contribution=proposes_defense and can never reach the exclusion branch. This column exists only to catch papers that propose nothing yet still feed the attack registry. Answer from the paper's section headings and tables, never from its genre.</t>
         </is>
       </c>
     </row>
